--- a/JsonConverter/ExcelFiles/Card.xlsx
+++ b/JsonConverter/ExcelFiles/Card.xlsx
@@ -12,70 +12,1048 @@
     <x:workbookView xWindow="0" yWindow="0" windowWidth="4294939905" windowHeight="17145"/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet name="DNTable_Weapon" sheetId="1" r:id="rId4"/>
+    <x:sheet name="Table_Card" sheetId="1" r:id="rId4"/>
   </x:sheets>
   <x:calcPr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" mc:Ignorable="hs" hs:hclCalcId="904"/>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="19">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="345">
+  <x:si>
+    <x:t>이중 타격</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사전 타격</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Grade</x:t>
+  </x:si>
+  <x:si>
+    <x:t>힘을 2 얻습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>판금을 4 얻습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피해를 32 줍니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이번 턴에, 다음에 사용하는 공격 카드가 1번 추가로 사용됩니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피해를 5 줍니다. 이번 전투 동안 체력을 잃은 횟수만큼 반복합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피해를 4 줍니다. 대상 적이 보유한 취약마다 피해량이 2 증가합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피해를 10 줍니다. 적이 보유한 취약이 2배로 증가합니다. 소멸.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피해를 9 줍니다. 이번 전투 동안 이 카드의 피해량이 5 증가합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피해를 6 줍니다. 공격이 아닌 카드를 뽑을 때까지 카드를 뽑습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피해를 12 줍니다. 다음에 사용하는 공격 카드의 비용이 0이 됩니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이번 턴에 공격 카드를 사용할 때마다, 방어도를 3 얻습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피해를 8 줍니다. 대상 적이 취약 상태라면, 2번 적중합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>매 턴마다 세 번째로 사용하는 공격 카드의 복사본을 1장 손으로 가져옵니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이름에 "타격"이 포함된 카드를 뽑을 때마다, 무작위 적에게 사용합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>카드를 3장 뽑습니다. 이번 턴 동안 더 이상 카드를 뽑을 수 없습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피해를 6 줍니다. 이 카드의 복사본 1장을 버린 카드 더미에 섞어 넣습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피해를 5만큼 2번 줍니다. 힘을 3 얻습니다. 대상 적이 힘을 1 얻습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>취약을 1 부여합니다. 대상 적이 보유한 취약마다 힘을 1 얻습니다. 소멸.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>적에게 받는 피해가 2배가 됩니다. 아군이 적에게 받는 피해가 절반이 됩니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수비</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피해를 7 줍니다. 이번 턴 동안 힘을 2 얻습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>체력을 1 잃습니다. 모든 적에게 피해를 9 줍니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>방어도를 7 얻습니다. 무작위 카드를 1장 소멸시킵니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>뽑을 카드 더미 맨 위의 카드를 사용한 뒤 소멸시킵니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피해를 18 줍니다. 무작위 카드를 1장 소멸 시킵니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>모든 적에게 피해를 4 주고 취약을 1 부여합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>뽑을 카드 더미 맨 위의 무작위 카드를 X장 사용합니다.</x:t>
+  </x:si>
   <x:si>
     <x:t>피해를 6 줍니다.</x:t>
   </x:si>
   <x:si>
+    <x:t>피해를 8 줍니다. 취약을 2 부여합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무작위 적에게 피해를 3만큼 3번 줍니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>방어도를 5 얻습니다. 피해를 5 줍니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피해를 9 줍니다. 카드를 1장 뽑습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>체력을 2 잃습니다. 피해를 15 줍니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>모든 적에게 피해를 5만큼 X번 줍니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
     <x:t>타격</x:t>
   </x:si>
   <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>박치기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>부메랑 칼날</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공격</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시작</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일반</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스킬</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고급</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파워</x:t>
+  </x:si>
+  <x:si>
+    <x:t>희귀</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피해를 15 줍니다. 이번 턴 동안 적이 힘을 10 잃습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>방어도를 5 얻습니다. 손에 있는 카드를 1장 강화합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>매 턴마다 처음으로 카드를 통해 얻는 방어도가 2배가 됩니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>카드를 2장 뽑습니다. 내 턴 시작 시, 뽑을 카드 더미 맨 위의 카드를 소멸시킵니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>방어도를 5 얻습니다. 이번 턴에 취약 상태의 적에게서 받는 피해량이 50% 감소합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내 턴 시작 시, 버린 카드 더미에서 무작위 공격 카드를 1장 손으로 가져오고 강화합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스킬 카드의 비용이 0이 됩니다. 스킬 카드를 사용할 때마다 그 카드를 소멸 시킵니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피해를 9 줍니다. 버린 카드 더미에서 카드를 1장 뽑을 카드 더미 맨 위에 놓습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>방어도를 8 얻습니다. 이번 턴 동안 소멸시킨 카드가 있다면 방어도를 추가로 8 얻습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>방어도를 12 얻습니다. 이번 턴에 공격을 받을 때마다, 공격한 적에게 피해를 4 줍니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cost</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int[]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
     <x:t>PrefabPath</x:t>
   </x:si>
   <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
     <x:t>TargetType</x:t>
   </x:si>
   <x:si>
-    <x:t>Cost</x:t>
-  </x:si>
-  <x:si>
     <x:t>CardType</x:t>
   </x:si>
   <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>attack</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피해를 9 줍니다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>single</x:t>
+    <x:t>피해를 20 줍니다. 취약을 5 부여합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>취약 상태의 적이 받는 피해가 25% 증가합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내 턴 시작 시 방어도가 사라지지 않습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>방어도를 8 얻습니다. 카드를 1장 뽑습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>체력을 2 잃습니다. 방어도를 16 얻습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>방어도를 7 얻습니다. 취약을 1 부여합니다.</x:t>
   </x:si>
   <x:si>
     <x:t>EffectValueList</x:t>
   </x:si>
   <x:si>
-    <x:t>int[]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>타격+</x:t>
+    <x:t>피해를 6 줍니다. 이름에 "타격"이 포함된 카드 1장당 피해량이 2 증가합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피해를 6 줍니다. 소멸된 카드 더미에 있는 카드 1장당 피해량이 3 증가합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>강타</x:t>
+  </x:si>
+  <x:si>
+    <x:t>분노</x:t>
+  </x:si>
+  <x:si>
+    <x:t>녹아내리는 주먹</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피해를 12 줍니다. 약화를 1 부여합니다. 취약을 1 부여합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>체력을 1 잃습니다. 카드를 1장 소멸시킵니다. 힘을 1 얻습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피해를 10 줍니다. 치명타라면, 최대 체력이 3 증가합니다. 소멸.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피해를 5 줍니다. 이번 턴 동안 체력을 잃었다면, 2번 적중합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정면 돌파</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피해를 5만큼 2번 줍니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>방어도만큼의 피해를 줍니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>방어도를 5 얻습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>방어도를 30 얻습니다. 소멸.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>취약을 3 부여합니다. 소멸.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내 턴 시작 시, 체력을 1 잃습니다. 내 턴 동안 체력을 잃을 때마다, 모든 적에게 피해를 6 줍니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고대의존재</x:t>
+  </x:si>
+  <x:si>
+    <x:t>멀티고급</x:t>
+  </x:si>
+  <x:si>
+    <x:t>멀티희귀</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무작위 공격 카드를 1장 손으로 가져옵니다. 이번 턴 동안 그 카드를 비용 없이 사용할 수 있습니다. 소멸.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>손에 있는 공격이 아닌 모든 카드를 소멸시킵니다. 소멸시킨 카드 1장당 방어도를 5 얻습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>손에 있는 공격 카드 1장당 에너지를 얻습니다. 이번 턴에 추가로 에너지를 얻을 수 없습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>체력을 1 잃습니다. 다른 플레이어에게 자신의 방어도와 동일한 만큼의 방어도를 줍니다. 소멸.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>모든 적에게 피해를 8 줍니다. 이번 턴에 사용한 다른 공격 카드 1장당 피해량이 2 증가합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소멸된 카드 더미에 카드가 3장 이상일 때만 사용할 수 있습니다. 모든 적에게 피해를 17 줍니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>모든 적에게 피해를 12 줍니다. 이번 턴 동안 사용한 공격 카드 1장당 비용이 1 감소합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>손에 있는 모든 카드를 소멸시킵니다. 소멸시킨 카드 1장당 무작위 카드 1장을 손으로 가져옵니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UpgradedCost</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_spite_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_bash_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_strike_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_anger_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_tremble_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_defend_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_cinder_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_havoc_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_inflame_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_fightme_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_pillage_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_rage_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_bully_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_taunt_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_stomp_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_rampage_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_evileye_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_brand_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_thrash_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_cascade_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_stoke_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_vicious_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_rupture_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_feed_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_mangle_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_inferno_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_notyet_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_pyre_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_break_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_tank_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_cruelty_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UpgradedEffectValueList</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_perfectedstrike_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_pommelstrike_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_bloodletting_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_swordboomerang_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_breakthrough_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_infernalblade_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_conflagration_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_howlfrombeyond_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_flamebarrier_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내 턴 시작 시, 힘을 2 얻습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_battletrance_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_drumofbattle_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_crimsonmantle_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_demonicshield_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_forgottenritual_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_expectafight_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1, 1, 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30, 7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2, 50</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6, 5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1, 3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5, 3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1, 10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4, 3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10, 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6, 4, 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1, 13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8, 50</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11, 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2, 20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11, 11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16, 6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7, 7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9, 9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3, 23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9, 3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3, 4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6, 4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15, 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2, 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20, 15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12, 2, 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피해를 4만큼 2번 줍니다. 손에 있는 무작위 공격 카드를 1장 소멸시키고, 그 카드의 피해량을 이 카드에 추가합니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>모든 적에게 피해를 16 줍니다. 내 턴 시작 시, 소멸된 카드 더미에서 사용됩니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>손에 있는 모든 카드를 소멸시킵니다. 소멸시킨 카드 1장당 피해를 7 줍니다. 소멸.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내 턴 종료 시, 손에 있는 무작위 공격 카드 1장이 무작위 적에게 사용됩니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>카드를 1장 소멸시킵니다. 카드를 2장 뽑습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>카드가 소멸될 때마다, 방어도를 3 얻습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>취약을 부여할 때마다, 카드를 1장 뽑습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>카드가 소멸될 때마다, 카드를 1장 뽑습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이번 턴에 카드를 소멸시켰다면, 에너지를 얻습니다. 소멸</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내 턴 시작 시, 체력을 1 잃고 방어도를 8 얻습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>손에 있는 모든 공격 카드를 거대한 바위로 변화시킵니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내 턴 동안 체력을 잃을 때마다, 힘을 1 얻습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>방어도를 얻을 때마다, 무작위 적에게 피해를 5 줍니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>체력을 6 잃습니다. 카드를 3장 뽑습니다. 소멸.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>저편의 울음소리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12, 1, 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>체력을 10 회복합니다. 소멸.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8, 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7, 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3, 3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몸통 박치기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2, 15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6, 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소용돌이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전투장비</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5, 5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>진정한 끈기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5, 3, 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5, 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몽둥이질</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12, 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전투 최면</x:t>
+  </x:si>
+  <x:si>
+    <x:t>덤벼라!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5, 50</x:t>
+  </x:si>
+  <x:si>
+    <x:t>철의 파동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>완벽한 타격</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8, 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기사회생</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7, 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1, 9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4, 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4, 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>폼멜 타격</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2, 16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9, 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>흘려보내기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피의 벽</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9, 5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>잿빛 타격</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6, 3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>조약의 끝</x:t>
+  </x:si>
+  <x:si>
+    <x:t>원시의 힘</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1, 8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불의 심장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8, 8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>싸움 준비</x:t>
+  </x:si>
+  <x:si>
+    <x:t>돌 갑옷</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3, 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10, 3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>요지부동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>잊힌 의식</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15, 10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불타는 조약</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1, 1, 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>악마의 눈</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12, 4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>핏빛 망토</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1, 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화력 증폭</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화염 장벽</x:t>
+  </x:si>
+  <x:si>
+    <x:t>갈가리 찢기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1, 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전투의 북소리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1, 6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어둠의 포옹</x:t>
+  </x:si>
+  <x:si>
+    <x:t>원투 펀치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3, 17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지옥검무</x:t>
+  </x:si>
+  <x:si>
+    <x:t>바리케이드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20, 5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>절대적인 힘</x:t>
+  </x:si>
+  <x:si>
+    <x:t>악마의 형상</x:t>
+  </x:si>
+  <x:si>
+    <x:t>악마의 방패</x:t>
+  </x:si>
+  <x:si>
+    <x:t>잿불</x:t>
+  </x:si>
+  <x:si>
+    <x:t>천둥</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사혈</x:t>
+  </x:si>
+  <x:si>
+    <x:t>떨림</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파괴</x:t>
+  </x:si>
+  <x:si>
+    <x:t>갈취</x:t>
+  </x:si>
+  <x:si>
+    <x:t>협박</x:t>
+  </x:si>
+  <x:si>
+    <x:t>악의</x:t>
+  </x:si>
+  <x:si>
+    <x:t>광란</x:t>
+  </x:si>
+  <x:si>
+    <x:t>어퍼컷</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무자비</x:t>
+  </x:si>
+  <x:si>
+    <x:t>혈류</x:t>
+  </x:si>
+  <x:si>
+    <x:t>해체</x:t>
+  </x:si>
+  <x:si>
+    <x:t>격노</x:t>
+  </x:si>
+  <x:si>
+    <x:t>짓밟기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>거상</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도발</x:t>
+  </x:si>
+  <x:si>
+    <x:t>제압</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지옥검</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무감각</x:t>
+  </x:si>
+  <x:si>
+    <x:t>발화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불바다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>쇄도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>포악함</x:t>
+  </x:si>
+  <x:si>
+    <x:t>저글링</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파열</x:t>
+  </x:si>
+  <x:si>
+    <x:t>난도질</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지옥불</x:t>
+  </x:si>
+  <x:si>
+    <x:t>난타</x:t>
+  </x:si>
+  <x:si>
+    <x:t>대화재</x:t>
+  </x:si>
+  <x:si>
+    <x:t>포식</x:t>
+  </x:si>
+  <x:si>
+    <x:t>제물</x:t>
+  </x:si>
+  <x:si>
+    <x:t>낙인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연쇄</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무적</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불굴</x:t>
+  </x:si>
+  <x:si>
+    <x:t>공격성</x:t>
+  </x:si>
+  <x:si>
+    <x:t>박살</x:t>
+  </x:si>
+  <x:si>
+    <x:t>타락</x:t>
+  </x:si>
+  <x:si>
+    <x:t>탱커</x:t>
+  </x:si>
+  <x:si>
+    <x:t>악랄함</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_bodyslam_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_twinstrike_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_thunderclap_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_setupstrike_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_moltenfist_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_headbutt_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_unrelenting_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_bloodwall_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_ashenstrike_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_hemokinesis_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_dismantle_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_ironwave_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_armaments_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_shrugitoff_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>체력을 3 잃고 에너지를 얻습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_truegrit_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_whirlwind_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_burningpact_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_bludgeon_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_colossus_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_feelnopain_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_stonearmor_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_juggling_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_dominate_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_uppercut_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_secondwind_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_aggression_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>매 턴 시작 시 에너지를 얻습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_tearasunder_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_pactsend_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_stampede_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_fiendfire_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_offering_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_onetwopunch_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_impervious_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_primalforce_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_hellraiser_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_barricade_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_unmovable_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_juggernaut_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_demonform_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_corruption_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>card_darkembrace_01</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -113,12 +1091,18 @@
       <x:sz val="10"/>
       <x:color rgb="ff000000"/>
     </x:font>
+    <x:font>
+      <x:name val="&quot;맑은 고딕&quot;"/>
+      <x:sz val="10"/>
+      <x:color rgb="ff000000"/>
+    </x:font>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
         <x:font hs:extension="1">
           <x:name val="&quot;맑은 고딕&quot;"/>
           <x:sz val="11"/>
           <x:color rgb="ff000000"/>
+          <x:b val="1"/>
           <hs:size val="100"/>
           <hs:ratio val="100"/>
           <hs:spacing val="0"/>
@@ -130,21 +1114,17 @@
           <x:name val="&quot;맑은 고딕&quot;"/>
           <x:sz val="11"/>
           <x:color rgb="ff000000"/>
+          <x:b val="1"/>
         </x:font>
       </mc:Fallback>
     </mc:AlternateContent>
     <x:font>
       <x:name val="&quot;맑은 고딕&quot;"/>
-      <x:sz val="10"/>
+      <x:sz val="11"/>
       <x:color rgb="ff000000"/>
     </x:font>
-    <x:font>
-      <x:name val="&quot;맑은 고딕&quot;"/>
-      <x:sz val="11"/>
-      <x:color rgb="ff008000"/>
-    </x:font>
   </x:fonts>
-  <x:fills count="8">
+  <x:fills count="3">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -153,42 +1133,12 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="ffcce5c4"/>
-        <x:bgColor indexed="64"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="ffcce5c4"/>
-        <x:bgColor rgb="ffc6efce"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="ffffffff"/>
-        <x:bgColor rgb="ff4d93d9"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="ffffffff"/>
-        <x:bgColor rgb="ffffc000"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="ffffffff"/>
-        <x:bgColor rgb="ffd86dcd"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="ffffffff"/>
+        <x:fgColor rgb="ffd4f6c2"/>
         <x:bgColor indexed="64"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="4">
+  <x:borders count="5">
     <x:border>
       <x:left>
         <x:color auto="1"/>
@@ -245,99 +1195,71 @@
         <x:color auto="1"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="medium">
+        <x:color rgb="ffc4c7c5"/>
+      </x:left>
+      <x:right style="medium">
+        <x:color rgb="ffc4c7c5"/>
+      </x:right>
+      <x:top style="medium">
+        <x:color rgb="ffc4c7c5"/>
+      </x:top>
+      <x:bottom style="medium">
+        <x:color rgb="ffc4c7c5"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="29">
+  <x:cellXfs count="15">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="left" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center"/>
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="left" vertical="bottom"/>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="left" vertical="bottom"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="left" vertical="bottom"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="left" vertical="bottom"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="left" vertical="bottom"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="left" vertical="bottom"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="left" vertical="bottom"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="left" vertical="bottom"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="left" vertical="bottom"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="left" vertical="bottom"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="left" vertical="bottom"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="left" vertical="bottom"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom"/>
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -943,462 +1865,2929 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:O35"/>
+  <x:dimension ref="A1:O101"/>
   <x:sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
-    <x:col min="1" max="1" width="23" style="3" customWidth="1"/>
-    <x:col min="2" max="2" width="19.5703125" style="4" customWidth="1"/>
-    <x:col min="3" max="3" width="50.7109375" style="4" customWidth="1"/>
-    <x:col min="4" max="4" width="12.5703125" style="8" bestFit="1" customWidth="1"/>
-    <x:col min="5" max="5" width="30.5703125" style="4" customWidth="1"/>
-    <x:col min="6" max="7" width="12.5703125" style="8"/>
-    <x:col min="8" max="8" width="16" style="8" customWidth="1"/>
-    <x:col min="9" max="9" width="12.5703125" style="8"/>
-    <x:col min="10" max="10" width="12.5703125" style="6"/>
+    <x:col min="1" max="1" width="27.4296875" style="2" customWidth="1"/>
+    <x:col min="2" max="2" width="19.5703125" style="3" customWidth="1"/>
+    <x:col min="3" max="3" width="43.85546875" style="3" customWidth="1"/>
+    <x:col min="4" max="4" width="8.28515625" style="7" customWidth="1"/>
+    <x:col min="5" max="5" width="12.71484375" style="3" customWidth="1"/>
+    <x:col min="6" max="6" width="18.85546875" style="7" customWidth="1"/>
+    <x:col min="7" max="7" width="12.5703125" style="6"/>
+    <x:col min="8" max="8" width="17.4296875" style="7" customWidth="1"/>
+    <x:col min="9" max="9" width="33.28515625" style="7" customWidth="1"/>
+    <x:col min="10" max="10" width="14.5703125" style="4" customWidth="1"/>
+    <x:col min="11" max="11" width="15.85546875" style="5" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A1" s="9" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B1" s="10"/>
-      <x:c r="C1" s="10"/>
-    </x:row>
-    <x:row r="2" spans="1:8" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A1" s="8" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B1" s="9"/>
+      <x:c r="C1" s="9"/>
+      <x:c r="D1" s="13"/>
+      <x:c r="E1" s="9"/>
+      <x:c r="F1" s="13"/>
+      <x:c r="G1" s="9"/>
+      <x:c r="H1" s="13"/>
+      <x:c r="I1" s="13"/>
+      <x:c r="J1" s="9"/>
+      <x:c r="K1" s="9"/>
+    </x:row>
+    <x:row r="2" spans="1:11" ht="15.75" customHeight="1">
       <x:c r="A2" s="9" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B2" s="10" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B2" s="9" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C2" s="9" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="D2" s="13" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="E2" s="9" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="F2" s="13" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="G2" s="9" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H2" s="13" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I2" s="13" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="J2" s="9" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="K2" s="9" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:11" s="11" customFormat="1" ht="15.75" customHeight="1">
+      <x:c r="A3" s="12" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B3" s="12" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="D3" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="E3" s="12" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="F3" s="14" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="G3" s="12" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H3" s="14" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="I3" s="14" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="J3" s="12" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="K3" s="12" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="A4" s="9" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="B4" s="9" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C4" s="9" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D4" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E4" s="9" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F4" s="13">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G4" s="9" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="H4" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I4" s="13">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C2" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D2" s="8" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E2" s="4" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F2" s="8" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="G2" s="8" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="H2" s="8" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:10" s="2" customFormat="1" ht="15.75" customHeight="1">
-      <x:c r="A3" s="11" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B3" s="12" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C3" s="12" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D3" s="5" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="E3" s="13" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F3" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G3" s="5" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H3" s="5" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I3" s="5"/>
-      <x:c r="J3" s="7"/>
-    </x:row>
-    <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A4" s="14"/>
-      <x:c r="B4" s="15" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="15" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D4" s="4">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E4" s="4" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="F4" s="4" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G4" s="4"/>
-      <x:c r="H4" s="4"/>
-      <x:c r="I4" s="4"/>
-      <x:c r="J4" s="16"/>
-      <x:c r="K4" s="1"/>
+      <x:c r="J4" s="9"/>
+      <x:c r="K4" s="9"/>
       <x:c r="L4" s="1"/>
       <x:c r="M4" s="1"/>
       <x:c r="N4" s="1"/>
       <x:c r="O4" s="1"/>
     </x:row>
     <x:row r="5" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A5" s="14"/>
-      <x:c r="B5" s="17" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C5" s="17" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D5" s="4">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E5" s="4" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="F5" s="4" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G5" s="4"/>
-      <x:c r="H5" s="4"/>
-      <x:c r="I5" s="4"/>
-      <x:c r="J5" s="16"/>
-      <x:c r="K5" s="1"/>
+      <x:c r="A5" s="9" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="B5" s="9" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C5" s="9" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="D5" s="13">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E5" s="9" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F5" s="13" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="G5" s="9" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="H5" s="13">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I5" s="13" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="J5" s="9"/>
+      <x:c r="K5" s="9"/>
       <x:c r="L5" s="1"/>
       <x:c r="M5" s="1"/>
       <x:c r="N5" s="1"/>
       <x:c r="O5" s="1"/>
     </x:row>
     <x:row r="6" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A6" s="18"/>
-      <x:c r="B6" s="17"/>
-      <x:c r="C6" s="17"/>
-      <x:c r="D6" s="4"/>
-      <x:c r="F6" s="4"/>
-      <x:c r="G6" s="4"/>
-      <x:c r="H6" s="4"/>
-      <x:c r="I6" s="4"/>
-      <x:c r="J6" s="16"/>
-      <x:c r="K6" s="1"/>
+      <x:c r="A6" s="9" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="B6" s="9" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C6" s="9" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D6" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E6" s="9" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F6" s="13">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G6" s="9" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I6" s="13">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J6" s="9"/>
+      <x:c r="K6" s="9"/>
       <x:c r="L6" s="1"/>
       <x:c r="M6" s="1"/>
       <x:c r="N6" s="1"/>
       <x:c r="O6" s="1"/>
     </x:row>
     <x:row r="7" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A7" s="14"/>
-      <x:c r="B7" s="15"/>
-      <x:c r="C7" s="15"/>
-      <x:c r="D7" s="4"/>
-      <x:c r="F7" s="4"/>
-      <x:c r="G7" s="4"/>
-      <x:c r="H7" s="4"/>
-      <x:c r="I7" s="4"/>
-      <x:c r="J7" s="16"/>
-      <x:c r="K7" s="1"/>
+      <x:c r="A7" s="9" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="B7" s="9" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="C7" s="9" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D7" s="13">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E7" s="9" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F7" s="13">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G7" s="9" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H7" s="13">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I7" s="13">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J7" s="9"/>
+      <x:c r="K7" s="9"/>
       <x:c r="L7" s="1"/>
       <x:c r="M7" s="1"/>
       <x:c r="N7" s="1"/>
       <x:c r="O7" s="1"/>
     </x:row>
     <x:row r="8" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A8" s="19"/>
-      <x:c r="B8" s="20"/>
-      <x:c r="C8" s="20"/>
-      <x:c r="D8" s="4"/>
-      <x:c r="F8" s="4"/>
-      <x:c r="G8" s="4"/>
-      <x:c r="H8" s="4"/>
-      <x:c r="I8" s="4"/>
-      <x:c r="J8" s="16"/>
-      <x:c r="K8" s="1"/>
+      <x:c r="A8" s="9" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="B8" s="9" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C8" s="9" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D8" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E8" s="9" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F8" s="13">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G8" s="9" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H8" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I8" s="13">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="J8" s="9"/>
+      <x:c r="K8" s="9"/>
       <x:c r="L8" s="1"/>
       <x:c r="M8" s="1"/>
       <x:c r="N8" s="1"/>
       <x:c r="O8" s="1"/>
     </x:row>
     <x:row r="9" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A9" s="19"/>
-      <x:c r="B9" s="20"/>
-      <x:c r="C9" s="20"/>
-      <x:c r="D9" s="4"/>
-      <x:c r="F9" s="4"/>
-      <x:c r="G9" s="4"/>
-      <x:c r="H9" s="4"/>
-      <x:c r="I9" s="4"/>
-      <x:c r="J9" s="16"/>
-      <x:c r="K9" s="1"/>
+      <x:c r="A9" s="9" t="s">
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="B9" s="9" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="C9" s="9" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D9" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E9" s="9" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F9" s="13">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G9" s="9" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H9" s="13">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I9" s="13">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J9" s="9"/>
+      <x:c r="K9" s="9"/>
       <x:c r="L9" s="1"/>
       <x:c r="M9" s="1"/>
       <x:c r="N9" s="1"/>
       <x:c r="O9" s="1"/>
     </x:row>
     <x:row r="10" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A10" s="21"/>
-      <x:c r="B10" s="22"/>
-      <x:c r="C10" s="22"/>
-      <x:c r="D10" s="4"/>
-      <x:c r="F10" s="4"/>
-      <x:c r="G10" s="4"/>
-      <x:c r="H10" s="4"/>
-      <x:c r="I10" s="4"/>
-      <x:c r="J10" s="16"/>
-      <x:c r="K10" s="1"/>
+      <x:c r="A10" s="9" t="s">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="B10" s="9" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C10" s="9" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="D10" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E10" s="9" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F10" s="13">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G10" s="9" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H10" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I10" s="13">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="J10" s="9"/>
+      <x:c r="K10" s="9"/>
       <x:c r="L10" s="1"/>
       <x:c r="M10" s="1"/>
       <x:c r="N10" s="1"/>
       <x:c r="O10" s="1"/>
     </x:row>
     <x:row r="11" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A11" s="21"/>
-      <x:c r="B11" s="22"/>
-      <x:c r="C11" s="22"/>
-      <x:c r="D11" s="4"/>
-      <x:c r="F11" s="4"/>
-      <x:c r="G11" s="4"/>
-      <x:c r="H11" s="4"/>
-      <x:c r="I11" s="4"/>
-      <x:c r="J11" s="16"/>
-      <x:c r="K11" s="1"/>
+      <x:c r="A11" s="9" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="B11" s="9" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C11" s="9" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D11" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E11" s="9" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F11" s="13" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="G11" s="9" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H11" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I11" s="13" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="J11" s="9"/>
+      <x:c r="K11" s="9"/>
       <x:c r="L11" s="1"/>
       <x:c r="M11" s="1"/>
       <x:c r="N11" s="1"/>
       <x:c r="O11" s="1"/>
     </x:row>
     <x:row r="12" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A12" s="19"/>
-      <x:c r="B12" s="20"/>
-      <x:c r="C12" s="20"/>
-      <x:c r="D12" s="4"/>
-      <x:c r="F12" s="4"/>
-      <x:c r="G12" s="4"/>
-      <x:c r="H12" s="4"/>
-      <x:c r="I12" s="4"/>
-      <x:c r="J12" s="16"/>
-      <x:c r="K12" s="1"/>
+      <x:c r="A12" s="9" t="s">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="B12" s="9" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C12" s="9" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="D12" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E12" s="9" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F12" s="13" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="G12" s="9" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H12" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I12" s="13" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="J12" s="9"/>
+      <x:c r="K12" s="9"/>
       <x:c r="L12" s="1"/>
       <x:c r="M12" s="1"/>
       <x:c r="N12" s="1"/>
       <x:c r="O12" s="1"/>
     </x:row>
     <x:row r="13" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A13" s="14"/>
-      <x:c r="B13" s="15"/>
-      <x:c r="C13" s="15"/>
-      <x:c r="D13" s="4"/>
-      <x:c r="F13" s="4"/>
-      <x:c r="G13" s="4"/>
-      <x:c r="H13" s="4"/>
-      <x:c r="I13" s="4"/>
-      <x:c r="J13" s="16"/>
-      <x:c r="K13" s="1"/>
+      <x:c r="A13" s="9" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="B13" s="9" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C13" s="9" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="D13" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E13" s="9" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F13" s="13" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="G13" s="9" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H13" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I13" s="13" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="J13" s="9"/>
+      <x:c r="K13" s="9"/>
       <x:c r="L13" s="1"/>
       <x:c r="M13" s="1"/>
       <x:c r="N13" s="1"/>
       <x:c r="O13" s="1"/>
     </x:row>
     <x:row r="14" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A14" s="21"/>
-      <x:c r="B14" s="22"/>
-      <x:c r="C14" s="22"/>
-      <x:c r="D14" s="4"/>
-      <x:c r="F14" s="4"/>
-      <x:c r="G14" s="4"/>
-      <x:c r="H14" s="4"/>
-      <x:c r="I14" s="4"/>
-      <x:c r="J14" s="16"/>
-      <x:c r="K14" s="1"/>
+      <x:c r="A14" s="9" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="B14" s="9" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="C14" s="9" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D14" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E14" s="9" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F14" s="13" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="G14" s="9" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H14" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I14" s="13" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="J14" s="9"/>
+      <x:c r="K14" s="9"/>
       <x:c r="L14" s="1"/>
       <x:c r="M14" s="1"/>
       <x:c r="N14" s="1"/>
       <x:c r="O14" s="1"/>
     </x:row>
     <x:row r="15" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A15" s="21"/>
-      <x:c r="B15" s="22"/>
-      <x:c r="C15" s="22"/>
-      <x:c r="D15" s="4"/>
-      <x:c r="F15" s="4"/>
-      <x:c r="G15" s="4"/>
-      <x:c r="H15" s="4"/>
-      <x:c r="I15" s="4"/>
-      <x:c r="J15" s="16"/>
-      <x:c r="K15" s="1"/>
+      <x:c r="A15" s="9" t="s">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="B15" s="9" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="C15" s="9" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D15" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E15" s="9" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F15" s="13" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="G15" s="9" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H15" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I15" s="13" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="J15" s="9"/>
+      <x:c r="K15" s="9"/>
       <x:c r="L15" s="1"/>
       <x:c r="M15" s="1"/>
       <x:c r="N15" s="1"/>
       <x:c r="O15" s="1"/>
     </x:row>
-    <x:row r="16" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A16" s="23"/>
-      <x:c r="B16" s="24"/>
-      <x:c r="C16" s="24"/>
-    </x:row>
-    <x:row r="17" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A17" s="23"/>
-      <x:c r="B17" s="24"/>
-      <x:c r="C17" s="24"/>
-    </x:row>
-    <x:row r="18" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A18" s="23"/>
-      <x:c r="B18" s="24"/>
-      <x:c r="C18" s="24"/>
-    </x:row>
-    <x:row r="19" spans="1:4" ht="15.75" customHeight="1">
-      <x:c r="A19" s="23"/>
-      <x:c r="B19" s="24"/>
-      <x:c r="C19" s="24"/>
-      <x:c r="D19" s="4"/>
-    </x:row>
-    <x:row r="20" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A20" s="23"/>
-      <x:c r="B20" s="24"/>
-      <x:c r="C20" s="24"/>
-    </x:row>
-    <x:row r="21" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A21" s="23"/>
-      <x:c r="B21" s="24"/>
-      <x:c r="C21" s="24"/>
-    </x:row>
-    <x:row r="22" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A22" s="23"/>
-      <x:c r="B22" s="24"/>
-      <x:c r="C22" s="24"/>
-    </x:row>
-    <x:row r="23" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A23" s="23"/>
-      <x:c r="B23" s="24"/>
-      <x:c r="C23" s="24"/>
-    </x:row>
-    <x:row r="24" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A24" s="23"/>
-      <x:c r="B24" s="24"/>
-      <x:c r="C24" s="24"/>
-    </x:row>
-    <x:row r="25" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A25" s="23"/>
-      <x:c r="B25" s="24"/>
-      <x:c r="C25" s="24"/>
-    </x:row>
-    <x:row r="26" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A26" s="25"/>
-      <x:c r="B26" s="26"/>
-      <x:c r="C26" s="26"/>
-    </x:row>
-    <x:row r="27" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A27" s="25"/>
-      <x:c r="B27" s="26"/>
-      <x:c r="C27" s="26"/>
-    </x:row>
-    <x:row r="28" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A28" s="25"/>
-      <x:c r="B28" s="26"/>
-      <x:c r="C28" s="26"/>
-    </x:row>
-    <x:row r="29" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A29" s="25"/>
-      <x:c r="B29" s="26"/>
-      <x:c r="C29" s="26"/>
-    </x:row>
-    <x:row r="30" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A30" s="25"/>
-      <x:c r="B30" s="26"/>
-      <x:c r="C30" s="26"/>
-    </x:row>
-    <x:row r="31" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A31" s="25"/>
-      <x:c r="B31" s="26"/>
-      <x:c r="C31" s="26"/>
-    </x:row>
-    <x:row r="32" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A32" s="27"/>
-      <x:c r="B32" s="28"/>
-      <x:c r="C32" s="28"/>
-    </x:row>
-    <x:row r="33" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A33" s="27"/>
-      <x:c r="B33" s="28"/>
-      <x:c r="C33" s="28"/>
-    </x:row>
-    <x:row r="34" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A34" s="27"/>
-      <x:c r="B34" s="28"/>
-      <x:c r="C34" s="28"/>
-    </x:row>
-    <x:row r="35" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A35" s="27"/>
-      <x:c r="B35" s="28"/>
-      <x:c r="C35" s="28"/>
-    </x:row>
-    <x:row r="36" ht="15.75" customHeight="1"/>
-    <x:row r="37" ht="15.75" customHeight="1"/>
-    <x:row r="38" ht="15.75" customHeight="1"/>
-    <x:row r="39" ht="15.75" customHeight="1"/>
-    <x:row r="40" ht="15.75" customHeight="1"/>
-    <x:row r="41" ht="15.75" customHeight="1"/>
-    <x:row r="42" ht="15.75" customHeight="1"/>
-    <x:row r="43" ht="15.75" customHeight="1"/>
-    <x:row r="44" ht="15.75" customHeight="1"/>
-    <x:row r="45" ht="15.75" customHeight="1"/>
-    <x:row r="46" ht="15.75" customHeight="1"/>
-    <x:row r="47" ht="15.75" customHeight="1"/>
-    <x:row r="48" ht="15.75" customHeight="1"/>
-    <x:row r="49" ht="15.75" customHeight="1"/>
-    <x:row r="50" ht="15.75" customHeight="1"/>
-    <x:row r="51" ht="15.75" customHeight="1"/>
-    <x:row r="52" ht="15.75" customHeight="1"/>
-    <x:row r="53" ht="15.75" customHeight="1"/>
-    <x:row r="54" ht="15.75" customHeight="1"/>
-    <x:row r="55" ht="15.75" customHeight="1"/>
-    <x:row r="56" ht="15.75" customHeight="1"/>
-    <x:row r="57" ht="15.75" customHeight="1"/>
-    <x:row r="58" ht="15.75" customHeight="1"/>
-    <x:row r="59" ht="15.75" customHeight="1"/>
-    <x:row r="60" ht="15.75" customHeight="1"/>
-    <x:row r="61" ht="15.75" customHeight="1"/>
-    <x:row r="62" ht="15.75" customHeight="1"/>
-    <x:row r="63" ht="15.75" customHeight="1"/>
-    <x:row r="64" ht="15.75" customHeight="1"/>
-    <x:row r="65" ht="15.75" customHeight="1"/>
-    <x:row r="66" ht="15.75" customHeight="1"/>
-    <x:row r="67" ht="15.75" customHeight="1"/>
-    <x:row r="68" ht="15.75" customHeight="1"/>
-    <x:row r="69" ht="15.75" customHeight="1"/>
-    <x:row r="70" ht="15.75" customHeight="1"/>
-    <x:row r="71" ht="15.75" customHeight="1"/>
-    <x:row r="72" ht="15.75" customHeight="1"/>
-    <x:row r="73" ht="15.75" customHeight="1"/>
-    <x:row r="74" ht="15.75" customHeight="1"/>
-    <x:row r="75" ht="15.75" customHeight="1"/>
-    <x:row r="76" ht="15.75" customHeight="1"/>
-    <x:row r="77" ht="15.75" customHeight="1"/>
-    <x:row r="78" ht="15.75" customHeight="1"/>
-    <x:row r="79" ht="15.75" customHeight="1"/>
-    <x:row r="80" ht="15.75" customHeight="1"/>
-    <x:row r="81" ht="15.75" customHeight="1"/>
-    <x:row r="82" ht="15.75" customHeight="1"/>
-    <x:row r="83" ht="15.75" customHeight="1"/>
-    <x:row r="84" ht="15.75" customHeight="1"/>
-    <x:row r="85" ht="15.75" customHeight="1"/>
-    <x:row r="86" ht="15.75" customHeight="1"/>
-    <x:row r="87" ht="15.75" customHeight="1"/>
-    <x:row r="88" ht="15.75" customHeight="1"/>
-    <x:row r="89" ht="15.75" customHeight="1"/>
-    <x:row r="90" ht="15.75" customHeight="1"/>
-    <x:row r="91" ht="15.75" customHeight="1"/>
-    <x:row r="92" ht="15.75" customHeight="1"/>
-    <x:row r="93" ht="15.75" customHeight="1"/>
-    <x:row r="94" ht="15.75" customHeight="1"/>
-    <x:row r="95" ht="15.75" customHeight="1"/>
-    <x:row r="96" ht="15.75" customHeight="1"/>
-    <x:row r="97" ht="15.75" customHeight="1"/>
-    <x:row r="98" ht="15.75" customHeight="1"/>
-    <x:row r="99" ht="15.75" customHeight="1"/>
-    <x:row r="100" ht="15.75" customHeight="1"/>
-    <x:row r="101" ht="15.75" customHeight="1"/>
+    <x:row r="16" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A16" s="9" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="B16" s="9" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="C16" s="9" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D16" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E16" s="9" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F16" s="13" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="G16" s="9" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H16" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I16" s="13" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="J16" s="9"/>
+      <x:c r="K16" s="9"/>
+    </x:row>
+    <x:row r="17" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A17" s="9" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="B17" s="9" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="C17" s="9" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D17" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E17" s="9" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F17" s="13" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="G17" s="9" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H17" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I17" s="13" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="J17" s="9"/>
+      <x:c r="K17" s="9"/>
+    </x:row>
+    <x:row r="18" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A18" s="9" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="B18" s="9" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="C18" s="9" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="D18" s="13">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E18" s="9" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F18" s="13" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="G18" s="9" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H18" s="13">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I18" s="13" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="J18" s="9"/>
+      <x:c r="K18" s="9"/>
+    </x:row>
+    <x:row r="19" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A19" s="9" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="B19" s="9" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="C19" s="9" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D19" s="13">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E19" s="9" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F19" s="13">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G19" s="9" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H19" s="13">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I19" s="13">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="J19" s="9"/>
+      <x:c r="K19" s="9"/>
+    </x:row>
+    <x:row r="20" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A20" s="9" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="B20" s="9" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="C20" s="9" t="s">
+        <x:v>316</x:v>
+      </x:c>
+      <x:c r="D20" s="13">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E20" s="9" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F20" s="13">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G20" s="9" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H20" s="13">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I20" s="13">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J20" s="9"/>
+      <x:c r="K20" s="9"/>
+    </x:row>
+    <x:row r="21" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A21" s="9" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="B21" s="9" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="C21" s="9" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D21" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E21" s="9" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F21" s="13">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G21" s="9" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H21" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I21" s="13">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="J21" s="9"/>
+      <x:c r="K21" s="9"/>
+    </x:row>
+    <x:row r="22" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A22" s="9" t="s">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="B22" s="9" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="C22" s="9" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D22" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E22" s="9" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F22" s="13">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G22" s="9" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H22" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I22" s="13">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J22" s="9"/>
+      <x:c r="K22" s="9"/>
+    </x:row>
+    <x:row r="23" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A23" s="9" t="s">
+        <x:v>317</x:v>
+      </x:c>
+      <x:c r="B23" s="9" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="C23" s="9" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D23" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E23" s="9" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F23" s="13">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G23" s="9" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H23" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I23" s="13">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J23" s="9"/>
+      <x:c r="K23" s="9"/>
+    </x:row>
+    <x:row r="24" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A24" s="9" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="B24" s="9" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="C24" s="9" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="D24" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E24" s="9" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F24" s="13">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G24" s="9" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H24" s="13">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I24" s="13">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J24" s="9"/>
+      <x:c r="K24" s="9"/>
+    </x:row>
+    <x:row r="25" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A25" s="9" t="s">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="B25" s="9" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="C25" s="9" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="D25" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E25" s="9" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F25" s="13" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="G25" s="9" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H25" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I25" s="13" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="J25" s="9"/>
+      <x:c r="K25" s="9"/>
+    </x:row>
+    <x:row r="26" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A26" s="9" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="B26" s="9" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="C26" s="9" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="D26" s="13">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E26" s="9" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F26" s="13" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="G26" s="9" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H26" s="13">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I26" s="13" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="J26" s="9"/>
+      <x:c r="K26" s="9"/>
+    </x:row>
+    <x:row r="27" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A27" s="9" t="s">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="B27" s="9" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="C27" s="9" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D27" s="13">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="E27" s="9" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F27" s="13">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G27" s="9" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H27" s="13">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="I27" s="13">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J27" s="9"/>
+      <x:c r="K27" s="9"/>
+    </x:row>
+    <x:row r="28" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A28" s="9" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="B28" s="9" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="C28" s="9" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="D28" s="13">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E28" s="9" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F28" s="13" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="G28" s="9" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H28" s="13">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I28" s="13" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="J28" s="9"/>
+      <x:c r="K28" s="9"/>
+    </x:row>
+    <x:row r="29" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A29" s="9" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="B29" s="9" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="C29" s="9" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D29" s="13">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E29" s="9" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F29" s="13" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="G29" s="9" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H29" s="13">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I29" s="13" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="J29" s="9"/>
+      <x:c r="K29" s="9"/>
+    </x:row>
+    <x:row r="30" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A30" s="9" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="B30" s="9" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="C30" s="9" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D30" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E30" s="9" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F30" s="13">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G30" s="9" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H30" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I30" s="13">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J30" s="9"/>
+      <x:c r="K30" s="9"/>
+    </x:row>
+    <x:row r="31" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A31" s="9" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="B31" s="9" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="C31" s="9" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D31" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E31" s="9" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F31" s="13" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="G31" s="9" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H31" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I31" s="13" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="J31" s="9"/>
+      <x:c r="K31" s="9"/>
+    </x:row>
+    <x:row r="32" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A32" s="9" t="s">
+        <x:v>310</x:v>
+      </x:c>
+      <x:c r="B32" s="9" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="C32" s="9" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="D32" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E32" s="9" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F32" s="13" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="G32" s="9" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H32" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I32" s="13" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="J32" s="9"/>
+      <x:c r="K32" s="9"/>
+    </x:row>
+    <x:row r="33" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A33" s="9" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="B33" s="9" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="C33" s="9" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D33" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E33" s="9" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F33" s="13" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="G33" s="9" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H33" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I33" s="13" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="J33" s="9"/>
+      <x:c r="K33" s="9"/>
+    </x:row>
+    <x:row r="34" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A34" s="9" t="s">
+        <x:v>311</x:v>
+      </x:c>
+      <x:c r="B34" s="9" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="C34" s="9" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D34" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E34" s="9" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F34" s="13" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="G34" s="9" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H34" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I34" s="13" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="J34" s="9"/>
+      <x:c r="K34" s="9"/>
+    </x:row>
+    <x:row r="35" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A35" s="9" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="B35" s="9" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="C35" s="9" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D35" s="13">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E35" s="9" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F35" s="13" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="G35" s="9" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H35" s="13">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I35" s="13" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="J35" s="9"/>
+      <x:c r="K35" s="9"/>
+    </x:row>
+    <x:row r="36" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A36" s="9" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="B36" s="9" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="C36" s="9" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D36" s="13">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E36" s="9" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F36" s="13">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G36" s="9" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H36" s="13">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I36" s="13">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="J36" s="9"/>
+      <x:c r="K36" s="9"/>
+    </x:row>
+    <x:row r="37" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A37" s="9" t="s">
+        <x:v>326</x:v>
+      </x:c>
+      <x:c r="B37" s="9" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="C37" s="9" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D37" s="13">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E37" s="9" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F37" s="13" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="G37" s="9" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H37" s="13">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I37" s="13" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="J37" s="9"/>
+      <x:c r="K37" s="9"/>
+    </x:row>
+    <x:row r="38" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A38" s="9" t="s">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="B38" s="9" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="C38" s="9" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D38" s="13">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E38" s="9" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F38" s="13">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G38" s="9" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H38" s="13">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I38" s="13">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="J38" s="9"/>
+      <x:c r="K38" s="9"/>
+    </x:row>
+    <x:row r="39" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A39" s="9" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="B39" s="9" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="C39" s="9" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="D39" s="13">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E39" s="9" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F39" s="13">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G39" s="9" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H39" s="13">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I39" s="13">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J39" s="9"/>
+      <x:c r="K39" s="9"/>
+    </x:row>
+    <x:row r="40" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A40" s="9" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="B40" s="9" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="C40" s="9" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="D40" s="13">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E40" s="9" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F40" s="13" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="G40" s="9" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H40" s="13">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I40" s="13" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="J40" s="9"/>
+      <x:c r="K40" s="9"/>
+    </x:row>
+    <x:row r="41" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A41" s="9" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="B41" s="9" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="C41" s="9" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D41" s="13">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E41" s="9" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F41" s="13">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G41" s="9" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H41" s="13">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I41" s="13">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J41" s="9"/>
+      <x:c r="K41" s="9"/>
+    </x:row>
+    <x:row r="42" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A42" s="9" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="B42" s="9" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="C42" s="9" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D42" s="13">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E42" s="9" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F42" s="13">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G42" s="9" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H42" s="13">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I42" s="13">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="J42" s="9"/>
+      <x:c r="K42" s="9"/>
+    </x:row>
+    <x:row r="43" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A43" s="9" t="s">
+        <x:v>321</x:v>
+      </x:c>
+      <x:c r="B43" s="9" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="C43" s="9" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D43" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E43" s="9" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F43" s="13" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="G43" s="9" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H43" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I43" s="13" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="J43" s="9"/>
+      <x:c r="K43" s="9"/>
+    </x:row>
+    <x:row r="44" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A44" s="9" t="s">
+        <x:v>327</x:v>
+      </x:c>
+      <x:c r="B44" s="9" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="C44" s="9" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D44" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E44" s="9" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F44" s="13">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G44" s="9" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H44" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I44" s="13">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="J44" s="9"/>
+      <x:c r="K44" s="9"/>
+    </x:row>
+    <x:row r="45" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A45" s="9" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="B45" s="9" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="C45" s="9" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="D45" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E45" s="9" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F45" s="13" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="G45" s="9" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H45" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I45" s="13" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="J45" s="9"/>
+      <x:c r="K45" s="9"/>
+    </x:row>
+    <x:row r="46" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A46" s="9" t="s">
+        <x:v>319</x:v>
+      </x:c>
+      <x:c r="B46" s="9" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="C46" s="9" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="D46" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E46" s="9" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F46" s="13" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="G46" s="9" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H46" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I46" s="13" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="J46" s="9"/>
+      <x:c r="K46" s="9"/>
+    </x:row>
+    <x:row r="47" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A47" s="9" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="B47" s="9" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="C47" s="9" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D47" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E47" s="9" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F47" s="13" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="G47" s="9" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H47" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I47" s="13" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="J47" s="9"/>
+      <x:c r="K47" s="9"/>
+    </x:row>
+    <x:row r="48" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A48" s="9" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="B48" s="9" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="C48" s="9" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="D48" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E48" s="9" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F48" s="13">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G48" s="9" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H48" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I48" s="13">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="J48" s="9"/>
+      <x:c r="K48" s="9"/>
+    </x:row>
+    <x:row r="49" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A49" s="9" t="s">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c r="B49" s="9" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="C49" s="9" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D49" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E49" s="9" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F49" s="13" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="G49" s="9" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H49" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I49" s="13" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="J49" s="9"/>
+      <x:c r="K49" s="9"/>
+    </x:row>
+    <x:row r="50" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A50" s="9" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="B50" s="9" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="C50" s="9" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="D50" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E50" s="9" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F50" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G50" s="9" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H50" s="13">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I50" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J50" s="9"/>
+      <x:c r="K50" s="9"/>
+    </x:row>
+    <x:row r="51" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A51" s="9" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="B51" s="9" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="C51" s="9" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="D51" s="13">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E51" s="9" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F51" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G51" s="9" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H51" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I51" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J51" s="9"/>
+      <x:c r="K51" s="9"/>
+    </x:row>
+    <x:row r="52" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A52" s="9" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="B52" s="9" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="C52" s="9" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="D52" s="13">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E52" s="9" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F52" s="13" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="G52" s="9" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H52" s="13">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I52" s="13" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="J52" s="9"/>
+      <x:c r="K52" s="9"/>
+    </x:row>
+    <x:row r="53" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A53" s="9" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="B53" s="9" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="C53" s="9" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D53" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E53" s="9" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="F53" s="13">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G53" s="9" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H53" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I53" s="13">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J53" s="9"/>
+      <x:c r="K53" s="9"/>
+    </x:row>
+    <x:row r="54" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A54" s="9" t="s">
+        <x:v>323</x:v>
+      </x:c>
+      <x:c r="B54" s="9" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="C54" s="9" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D54" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E54" s="9" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="F54" s="13">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G54" s="9" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H54" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I54" s="13">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="J54" s="9"/>
+      <x:c r="K54" s="9"/>
+    </x:row>
+    <x:row r="55" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A55" s="9" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="B55" s="9" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="C55" s="9" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="D55" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E55" s="9" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="F55" s="13">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G55" s="9" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H55" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I55" s="13">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="J55" s="9"/>
+      <x:c r="K55" s="9"/>
+    </x:row>
+    <x:row r="56" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A56" s="9" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="B56" s="9" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="C56" s="9" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D56" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E56" s="9" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="F56" s="13">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G56" s="9" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H56" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I56" s="13">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J56" s="9"/>
+      <x:c r="K56" s="9"/>
+    </x:row>
+    <x:row r="57" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A57" s="9" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="B57" s="9" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="C57" s="9" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D57" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E57" s="9" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="F57" s="13" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="G57" s="9" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H57" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I57" s="13" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="J57" s="9"/>
+      <x:c r="K57" s="9"/>
+    </x:row>
+    <x:row r="58" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A58" s="9" t="s">
+        <x:v>324</x:v>
+      </x:c>
+      <x:c r="B58" s="9" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="C58" s="9" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D58" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E58" s="9" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="F58" s="13" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="G58" s="9" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H58" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I58" s="13" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="J58" s="9"/>
+      <x:c r="K58" s="9"/>
+    </x:row>
+    <x:row r="59" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A59" s="9" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="B59" s="9" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="C59" s="9" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="D59" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E59" s="9" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="F59" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G59" s="9" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H59" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I59" s="13">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J59" s="9"/>
+      <x:c r="K59" s="9"/>
+    </x:row>
+    <x:row r="60" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A60" s="9" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="B60" s="9" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="C60" s="9" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="D60" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E60" s="9" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="F60" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G60" s="9" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H60" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I60" s="13">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J60" s="9"/>
+      <x:c r="K60" s="9"/>
+    </x:row>
+    <x:row r="61" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A61" s="9" t="s">
+        <x:v>332</x:v>
+      </x:c>
+      <x:c r="B61" s="9" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="C61" s="9" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="D61" s="13">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E61" s="9" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="F61" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G61" s="9" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="H61" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I61" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J61" s="9"/>
+      <x:c r="K61" s="9"/>
+    </x:row>
+    <x:row r="62" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A62" s="9" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="B62" s="9" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="C62" s="9" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D62" s="13">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E62" s="9" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F62" s="13" t="s">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="G62" s="9" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H62" s="13">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I62" s="13" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="J62" s="9"/>
+      <x:c r="K62" s="9"/>
+    </x:row>
+    <x:row r="63" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A63" s="9" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="B63" s="9" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="C63" s="9" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="D63" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E63" s="9" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F63" s="13" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="G63" s="9" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H63" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I63" s="13" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="J63" s="9"/>
+      <x:c r="K63" s="9"/>
+    </x:row>
+    <x:row r="64" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A64" s="9" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="B64" s="9" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="C64" s="9" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D64" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E64" s="9" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F64" s="13" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="G64" s="9" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H64" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I64" s="13" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="J64" s="9"/>
+      <x:c r="K64" s="9"/>
+    </x:row>
+    <x:row r="65" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A65" s="9" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="B65" s="9" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="C65" s="9" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="D65" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E65" s="9" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F65" s="13" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="G65" s="9" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H65" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I65" s="13" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="J65" s="9"/>
+      <x:c r="K65" s="9"/>
+    </x:row>
+    <x:row r="66" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A66" s="9" t="s">
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="B66" s="9" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="C66" s="9" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D66" s="13">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E66" s="9" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F66" s="13">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G66" s="9" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H66" s="13">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I66" s="13">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="J66" s="9"/>
+      <x:c r="K66" s="9"/>
+    </x:row>
+    <x:row r="67" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A67" s="9" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="B67" s="9" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="C67" s="9" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="D67" s="13">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E67" s="9" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F67" s="13">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G67" s="9" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H67" s="13">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I67" s="13">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="J67" s="9"/>
+      <x:c r="K67" s="9"/>
+    </x:row>
+    <x:row r="68" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A68" s="9" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="B68" s="9" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="C68" s="9" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D68" s="13">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E68" s="9" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F68" s="13" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="G68" s="9" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H68" s="13">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I68" s="13" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="J68" s="9"/>
+      <x:c r="K68" s="9"/>
+    </x:row>
+    <x:row r="69" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A69" s="9" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="B69" s="9" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="C69" s="9" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="D69" s="13">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E69" s="9" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F69" s="13" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="G69" s="9" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H69" s="13">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I69" s="13" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="J69" s="9"/>
+      <x:c r="K69" s="9"/>
+    </x:row>
+    <x:row r="70" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A70" s="9" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="B70" s="9" t="s">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="C70" s="9" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D70" s="13">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="E70" s="9" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F70" s="13">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="G70" s="9" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H70" s="13">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="I70" s="13">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="J70" s="9"/>
+      <x:c r="K70" s="9"/>
+    </x:row>
+    <x:row r="71" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A71" s="9" t="s">
+        <x:v>337</x:v>
+      </x:c>
+      <x:c r="B71" s="9" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="C71" s="9" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="D71" s="13">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E71" s="9" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F71" s="13">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G71" s="9" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H71" s="13">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I71" s="13">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J71" s="9"/>
+      <x:c r="K71" s="9"/>
+    </x:row>
+    <x:row r="72" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A72" s="9" t="s">
+        <x:v>334</x:v>
+      </x:c>
+      <x:c r="B72" s="9" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="C72" s="9" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="D72" s="13">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E72" s="9" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F72" s="13" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="G72" s="9" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H72" s="13">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I72" s="13" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="J72" s="9"/>
+      <x:c r="K72" s="9"/>
+    </x:row>
+    <x:row r="73" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A73" s="9" t="s">
+        <x:v>335</x:v>
+      </x:c>
+      <x:c r="B73" s="9" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="C73" s="9" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D73" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E73" s="9" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F73" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G73" s="9" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H73" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I73" s="13">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J73" s="9"/>
+      <x:c r="K73" s="9"/>
+    </x:row>
+    <x:row r="74" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A74" s="9" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="B74" s="9" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="C74" s="9" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="D74" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E74" s="9" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F74" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G74" s="9" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H74" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I74" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J74" s="9"/>
+      <x:c r="K74" s="9"/>
+    </x:row>
+    <x:row r="75" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A75" s="9" t="s">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="B75" s="9" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="C75" s="9" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D75" s="13">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E75" s="9" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F75" s="13">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G75" s="9" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H75" s="13">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I75" s="13">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="J75" s="9"/>
+      <x:c r="K75" s="9"/>
+    </x:row>
+    <x:row r="76" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A76" s="9" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="B76" s="9" t="s">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="C76" s="9" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="D76" s="13">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E76" s="9" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F76" s="13">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G76" s="9" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H76" s="13">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I76" s="13">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="J76" s="9"/>
+      <x:c r="K76" s="9"/>
+    </x:row>
+    <x:row r="77" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A77" s="9" t="s">
+        <x:v>328</x:v>
+      </x:c>
+      <x:c r="B77" s="9" t="s">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="C77" s="9" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="D77" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E77" s="9" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="F77" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G77" s="9" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H77" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I77" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J77" s="9"/>
+      <x:c r="K77" s="9"/>
+    </x:row>
+    <x:row r="78" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A78" s="9" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="B78" s="9" t="s">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="C78" s="9" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D78" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E78" s="9" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="F78" s="13">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="G78" s="9" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H78" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I78" s="13">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="J78" s="9"/>
+      <x:c r="K78" s="9"/>
+    </x:row>
+    <x:row r="79" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A79" s="9" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="B79" s="9" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="C79" s="9" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="D79" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E79" s="9" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="F79" s="13" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="G79" s="9" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H79" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I79" s="13" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="J79" s="9"/>
+      <x:c r="K79" s="9"/>
+    </x:row>
+    <x:row r="80" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A80" s="9" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="B80" s="9" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="C80" s="9" t="s">
+        <x:v>329</x:v>
+      </x:c>
+      <x:c r="D80" s="13">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E80" s="9" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="F80" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G80" s="9" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H80" s="13">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I80" s="13">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J80" s="9"/>
+      <x:c r="K80" s="9"/>
+    </x:row>
+    <x:row r="81" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A81" s="9" t="s">
+        <x:v>344</x:v>
+      </x:c>
+      <x:c r="B81" s="9" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="C81" s="9" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="D81" s="13">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E81" s="9" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="F81" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G81" s="9" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H81" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I81" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J81" s="9"/>
+      <x:c r="K81" s="9"/>
+    </x:row>
+    <x:row r="82" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A82" s="9" t="s">
+        <x:v>340</x:v>
+      </x:c>
+      <x:c r="B82" s="9" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="C82" s="9" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D82" s="13">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E82" s="9" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="F82" s="13">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G82" s="9" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H82" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I82" s="13">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J82" s="9"/>
+      <x:c r="K82" s="9"/>
+    </x:row>
+    <x:row r="83" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A83" s="9" t="s">
+        <x:v>341</x:v>
+      </x:c>
+      <x:c r="B83" s="9" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="C83" s="9" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="D83" s="13">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E83" s="9" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="F83" s="13">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G83" s="9" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H83" s="13">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I83" s="13">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="J83" s="9"/>
+      <x:c r="K83" s="9"/>
+    </x:row>
+    <x:row r="84" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A84" s="9" t="s">
+        <x:v>338</x:v>
+      </x:c>
+      <x:c r="B84" s="9" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="C84" s="9" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D84" s="13">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E84" s="9" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="F84" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G84" s="9" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H84" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I84" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J84" s="9"/>
+      <x:c r="K84" s="9"/>
+    </x:row>
+    <x:row r="85" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A85" s="9" t="s">
+        <x:v>339</x:v>
+      </x:c>
+      <x:c r="B85" s="9" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="C85" s="9" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="D85" s="13">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E85" s="9" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="F85" s="13">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G85" s="9" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H85" s="13">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I85" s="13">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J85" s="9"/>
+      <x:c r="K85" s="9"/>
+    </x:row>
+    <x:row r="86" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A86" s="9" t="s">
+        <x:v>342</x:v>
+      </x:c>
+      <x:c r="B86" s="9" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="C86" s="9" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="D86" s="13">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E86" s="9" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="F86" s="13">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G86" s="9" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="H86" s="13">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I86" s="13">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J86" s="9"/>
+      <x:c r="K86" s="9"/>
+    </x:row>
+    <x:row r="87" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A87" s="9" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="B87" s="9" t="s">
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="C87" s="9" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D87" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E87" s="9" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F87" s="13" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="G87" s="9" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="H87" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I87" s="13" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="J87" s="9"/>
+      <x:c r="K87" s="9"/>
+    </x:row>
+    <x:row r="88" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A88" s="9" t="s">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="B88" s="9" t="s">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="C88" s="9" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="D88" s="13">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E88" s="9" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="F88" s="13">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G88" s="9" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="H88" s="13">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I88" s="13">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J88" s="9"/>
+      <x:c r="K88" s="9"/>
+    </x:row>
+    <x:row r="89" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A89" s="9" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="B89" s="9" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="C89" s="9" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D89" s="13">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E89" s="9" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F89" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G89" s="9" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="H89" s="13">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I89" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J89" s="9"/>
+      <x:c r="K89" s="9"/>
+    </x:row>
+    <x:row r="90" spans="1:11" ht="15.75" customHeight="1">
+      <x:c r="A90" s="9" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="B90" s="9" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="C90" s="9" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D90" s="13">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E90" s="9" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F90" s="13" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="G90" s="9" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="H90" s="13">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I90" s="13" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="J90" s="10"/>
+      <x:c r="K90" s="10"/>
+    </x:row>
+    <x:row r="91" spans="2:7" ht="15.75" customHeight="1">
+      <x:c r="B91" s="8"/>
+      <x:c r="D91" s="13"/>
+      <x:c r="E91" s="9"/>
+      <x:c r="F91" s="13"/>
+      <x:c r="G91" s="9"/>
+    </x:row>
+    <x:row r="92" spans="2:7" ht="15.75" customHeight="1">
+      <x:c r="B92" s="8"/>
+      <x:c r="D92" s="13"/>
+      <x:c r="E92" s="9"/>
+      <x:c r="F92" s="13"/>
+      <x:c r="G92" s="9"/>
+    </x:row>
+    <x:row r="93" spans="2:7" ht="15.75" customHeight="1">
+      <x:c r="B93" s="8"/>
+      <x:c r="D93" s="13"/>
+      <x:c r="E93" s="9"/>
+      <x:c r="F93" s="13"/>
+      <x:c r="G93" s="9"/>
+    </x:row>
+    <x:row r="94" spans="2:7" ht="15.75" customHeight="1">
+      <x:c r="B94" s="8"/>
+      <x:c r="D94" s="13"/>
+      <x:c r="E94" s="9"/>
+      <x:c r="F94" s="13"/>
+      <x:c r="G94" s="9"/>
+    </x:row>
+    <x:row r="95" spans="2:7" ht="15.75" customHeight="1">
+      <x:c r="B95" s="8"/>
+      <x:c r="D95" s="13"/>
+      <x:c r="E95" s="9"/>
+      <x:c r="F95" s="13"/>
+      <x:c r="G95" s="9"/>
+    </x:row>
+    <x:row r="96" spans="2:7" ht="15.75" customHeight="1">
+      <x:c r="B96" s="8"/>
+      <x:c r="D96" s="13"/>
+      <x:c r="E96" s="9"/>
+      <x:c r="F96" s="13"/>
+      <x:c r="G96" s="9"/>
+    </x:row>
+    <x:row r="97" spans="2:7" ht="15.75" customHeight="1">
+      <x:c r="B97" s="8"/>
+      <x:c r="D97" s="13"/>
+      <x:c r="E97" s="9"/>
+      <x:c r="F97" s="13"/>
+      <x:c r="G97" s="9"/>
+    </x:row>
+    <x:row r="98" spans="2:7" ht="15.75" customHeight="1">
+      <x:c r="B98" s="8"/>
+      <x:c r="D98" s="13"/>
+      <x:c r="E98" s="9"/>
+      <x:c r="F98" s="13"/>
+      <x:c r="G98" s="9"/>
+    </x:row>
+    <x:row r="99" spans="2:7" ht="15.75" customHeight="1">
+      <x:c r="B99" s="8"/>
+      <x:c r="D99" s="13"/>
+      <x:c r="E99" s="9"/>
+      <x:c r="F99" s="13"/>
+      <x:c r="G99" s="9"/>
+    </x:row>
+    <x:row r="100" spans="2:7" ht="15.75" customHeight="1">
+      <x:c r="B100" s="8"/>
+      <x:c r="D100" s="13"/>
+      <x:c r="E100" s="9"/>
+      <x:c r="F100" s="13"/>
+      <x:c r="G100" s="9"/>
+    </x:row>
+    <x:row r="101" spans="2:7" ht="15.75" customHeight="1">
+      <x:c r="B101" s="8"/>
+      <x:c r="D101" s="13"/>
+      <x:c r="E101" s="9"/>
+      <x:c r="F101" s="13"/>
+      <x:c r="G101" s="9"/>
+    </x:row>
     <x:row r="102" ht="15.75" customHeight="1"/>
     <x:row r="103" ht="15.75" customHeight="1"/>
     <x:row r="104" ht="15.75" customHeight="1"/>
@@ -2299,7 +5688,7 @@
     <x:row r="999" ht="15.75" customHeight="1"/>
     <x:row r="1000" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:pageMargins left="0.69999998807907104" right="0.69999998807907104" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
+  <x:pageMargins left="0.69986110925674438" right="0.69986110925674438" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/Card.xlsx
+++ b/JsonConverter/ExcelFiles/Card.xlsx
@@ -12,7 +12,7 @@
     <x:workbookView xWindow="0" yWindow="0" windowWidth="4294939905" windowHeight="17145"/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet name="Table_Card" sheetId="1" r:id="rId4"/>
+    <x:sheet name="Table_WarriorCard" sheetId="1" r:id="rId4"/>
   </x:sheets>
   <x:calcPr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" mc:Ignorable="hs" hs:hclCalcId="904"/>
 </x:workbook>
